--- a/Part B(2) BoM.xlsx
+++ b/Part B(2) BoM.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6D8959-FC93-48FD-BAB7-EBD724ACBFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="3072" yWindow="3072" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Part B(2) BoM" state="visible" r:id="rId4"/>
+    <sheet name="Part B(2) BoM" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="188">
   <si>
     <t>No.</t>
   </si>
@@ -551,21 +555,6 @@
   </si>
   <si>
     <t>C7429910</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>红色LED</t>
-  </si>
-  <si>
-    <t>U23</t>
-  </si>
-  <si>
-    <t>LED-SMD_L2.2-W1.6-FD_G2016C</t>
-  </si>
-  <si>
-    <t>C9900005314</t>
   </si>
   <si>
     <t>26</t>
@@ -595,14 +584,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -965,14 +954,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1010,7 +999,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1048,7 +1037,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1086,7 +1075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1124,7 +1113,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1162,7 +1151,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -1200,7 +1189,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -1238,7 +1227,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -1276,7 +1265,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -1314,7 +1303,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -1352,7 +1341,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>76</v>
       </c>
@@ -1390,7 +1379,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>85</v>
       </c>
@@ -1428,7 +1417,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -1466,7 +1455,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>99</v>
       </c>
@@ -1504,7 +1493,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>106</v>
       </c>
@@ -1542,7 +1531,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>113</v>
       </c>
@@ -1580,7 +1569,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>119</v>
       </c>
@@ -1618,7 +1607,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>124</v>
       </c>
@@ -1656,7 +1645,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>133</v>
       </c>
@@ -1694,7 +1683,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>140</v>
       </c>
@@ -1732,7 +1721,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>148</v>
       </c>
@@ -1770,7 +1759,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>154</v>
       </c>
@@ -1808,7 +1797,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>160</v>
       </c>
@@ -1846,7 +1835,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>168</v>
       </c>
@@ -1884,7 +1873,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>174</v>
       </c>
@@ -1922,7 +1911,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>180</v>
       </c>
@@ -1945,60 +1934,22 @@
         <v>181</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>184</v>
       </c>
       <c r="I26" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J26" t="s">
         <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="L26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>185</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>186</v>
-      </c>
-      <c r="D27" t="s">
         <v>187</v>
       </c>
-      <c r="E27" t="s">
-        <v>188</v>
-      </c>
-      <c r="F27" t="s">
-        <v>16</v>
-      </c>
-      <c r="G27" t="s">
-        <v>186</v>
-      </c>
-      <c r="H27" t="s">
-        <v>189</v>
-      </c>
-      <c r="I27" t="s">
-        <v>190</v>
-      </c>
-      <c r="J27" t="s">
-        <v>25</v>
-      </c>
-      <c r="K27" t="s">
-        <v>191</v>
-      </c>
-      <c r="L27" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -2006,6 +1957,6 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>